--- a/Calculos 2 Datasets.xlsx
+++ b/Calculos 2 Datasets.xlsx
@@ -23,6 +23,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Kruskal" sheetId="14" state="visible" r:id="rId14"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-Prim" sheetId="15" state="visible" r:id="rId15"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="B-MST Resumen" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas MST A" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rutas MST B" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad rVP" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -160,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -231,6 +234,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12129,15 +12137,15 @@
           <t>x1 — x2</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="26" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -12357,14 +12365,14 @@
           <t>IM(x1,x2) =</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="27" t="n"/>
       <c r="J10" s="11">
         <f>SUM(J6:J9)</f>
         <v/>
@@ -12376,15 +12384,15 @@
           <t>x1 — x5</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -12684,14 +12692,14 @@
           <t>IM(x1,x5) =</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="26" t="n"/>
+      <c r="I21" s="27" t="n"/>
       <c r="J21" s="11">
         <f>SUM(J15:J20)</f>
         <v/>
@@ -12703,15 +12711,15 @@
           <t>x1 — x4</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -12931,14 +12939,14 @@
           <t>IM(x1,x4) =</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="27" t="n"/>
       <c r="J30" s="11">
         <f>SUM(J26:J29)</f>
         <v/>
@@ -12950,15 +12958,15 @@
           <t>x1 — x6</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="n"/>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -13178,14 +13186,14 @@
           <t>IM(x1,x6) =</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="26" t="n"/>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="27" t="n"/>
       <c r="J39" s="11">
         <f>SUM(J35:J38)</f>
         <v/>
@@ -13197,15 +13205,15 @@
           <t>x1 — x9</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="26" t="n"/>
+      <c r="G42" s="26" t="n"/>
+      <c r="H42" s="26" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="27" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -13585,14 +13593,14 @@
           <t>IM(x1,x9) =</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
+      <c r="B52" s="26" t="n"/>
+      <c r="C52" s="26" t="n"/>
+      <c r="D52" s="26" t="n"/>
+      <c r="E52" s="26" t="n"/>
+      <c r="F52" s="26" t="n"/>
+      <c r="G52" s="26" t="n"/>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="27" t="n"/>
       <c r="J52" s="11">
         <f>SUM(J44:J51)</f>
         <v/>
@@ -13604,15 +13612,15 @@
           <t>x1 — x3</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="26" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
+      <c r="G55" s="26" t="n"/>
+      <c r="H55" s="26" t="n"/>
+      <c r="I55" s="26" t="n"/>
+      <c r="J55" s="27" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -13832,14 +13840,14 @@
           <t>IM(x1,x3) =</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
+      <c r="B61" s="26" t="n"/>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n"/>
+      <c r="G61" s="26" t="n"/>
+      <c r="H61" s="26" t="n"/>
+      <c r="I61" s="27" t="n"/>
       <c r="J61" s="11">
         <f>SUM(J57:J60)</f>
         <v/>
@@ -13851,15 +13859,15 @@
           <t>x2 — x5</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
+      <c r="B64" s="26" t="n"/>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="26" t="n"/>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="26" t="n"/>
+      <c r="G64" s="26" t="n"/>
+      <c r="H64" s="26" t="n"/>
+      <c r="I64" s="26" t="n"/>
+      <c r="J64" s="27" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -14159,14 +14167,14 @@
           <t>IM(x2,x5) =</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
+      <c r="B72" s="26" t="n"/>
+      <c r="C72" s="26" t="n"/>
+      <c r="D72" s="26" t="n"/>
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="26" t="n"/>
+      <c r="G72" s="26" t="n"/>
+      <c r="H72" s="26" t="n"/>
+      <c r="I72" s="27" t="n"/>
       <c r="J72" s="11">
         <f>SUM(J66:J71)</f>
         <v/>
@@ -14178,15 +14186,15 @@
           <t>x2 — x4</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
+      <c r="B75" s="26" t="n"/>
+      <c r="C75" s="26" t="n"/>
+      <c r="D75" s="26" t="n"/>
+      <c r="E75" s="26" t="n"/>
+      <c r="F75" s="26" t="n"/>
+      <c r="G75" s="26" t="n"/>
+      <c r="H75" s="26" t="n"/>
+      <c r="I75" s="26" t="n"/>
+      <c r="J75" s="27" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -14406,14 +14414,14 @@
           <t>IM(x2,x4) =</t>
         </is>
       </c>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="27" t="n"/>
       <c r="J81" s="11">
         <f>SUM(J77:J80)</f>
         <v/>
@@ -14425,15 +14433,15 @@
           <t>x2 — x6</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
+      <c r="B84" s="26" t="n"/>
+      <c r="C84" s="26" t="n"/>
+      <c r="D84" s="26" t="n"/>
+      <c r="E84" s="26" t="n"/>
+      <c r="F84" s="26" t="n"/>
+      <c r="G84" s="26" t="n"/>
+      <c r="H84" s="26" t="n"/>
+      <c r="I84" s="26" t="n"/>
+      <c r="J84" s="27" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -14653,14 +14661,14 @@
           <t>IM(x2,x6) =</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="26" t="n"/>
+      <c r="G90" s="26" t="n"/>
+      <c r="H90" s="26" t="n"/>
+      <c r="I90" s="27" t="n"/>
       <c r="J90" s="11">
         <f>SUM(J86:J89)</f>
         <v/>
@@ -14672,15 +14680,15 @@
           <t>x2 — x9</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
+      <c r="B93" s="26" t="n"/>
+      <c r="C93" s="26" t="n"/>
+      <c r="D93" s="26" t="n"/>
+      <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
+      <c r="G93" s="26" t="n"/>
+      <c r="H93" s="26" t="n"/>
+      <c r="I93" s="26" t="n"/>
+      <c r="J93" s="27" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -15060,14 +15068,14 @@
           <t>IM(x2,x9) =</t>
         </is>
       </c>
-      <c r="B103" s="10" t="n"/>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
+      <c r="B103" s="26" t="n"/>
+      <c r="C103" s="26" t="n"/>
+      <c r="D103" s="26" t="n"/>
+      <c r="E103" s="26" t="n"/>
+      <c r="F103" s="26" t="n"/>
+      <c r="G103" s="26" t="n"/>
+      <c r="H103" s="26" t="n"/>
+      <c r="I103" s="27" t="n"/>
       <c r="J103" s="11">
         <f>SUM(J95:J102)</f>
         <v/>
@@ -15079,15 +15087,15 @@
           <t>x2 — x3</t>
         </is>
       </c>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="5" t="n"/>
+      <c r="B106" s="26" t="n"/>
+      <c r="C106" s="26" t="n"/>
+      <c r="D106" s="26" t="n"/>
+      <c r="E106" s="26" t="n"/>
+      <c r="F106" s="26" t="n"/>
+      <c r="G106" s="26" t="n"/>
+      <c r="H106" s="26" t="n"/>
+      <c r="I106" s="26" t="n"/>
+      <c r="J106" s="27" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -15307,14 +15315,14 @@
           <t>IM(x2,x3) =</t>
         </is>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
+      <c r="B112" s="26" t="n"/>
+      <c r="C112" s="26" t="n"/>
+      <c r="D112" s="26" t="n"/>
+      <c r="E112" s="26" t="n"/>
+      <c r="F112" s="26" t="n"/>
+      <c r="G112" s="26" t="n"/>
+      <c r="H112" s="26" t="n"/>
+      <c r="I112" s="27" t="n"/>
       <c r="J112" s="11">
         <f>SUM(J108:J111)</f>
         <v/>
@@ -15326,15 +15334,15 @@
           <t>x5 — x4</t>
         </is>
       </c>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="5" t="n"/>
-      <c r="H115" s="5" t="n"/>
-      <c r="I115" s="5" t="n"/>
-      <c r="J115" s="5" t="n"/>
+      <c r="B115" s="26" t="n"/>
+      <c r="C115" s="26" t="n"/>
+      <c r="D115" s="26" t="n"/>
+      <c r="E115" s="26" t="n"/>
+      <c r="F115" s="26" t="n"/>
+      <c r="G115" s="26" t="n"/>
+      <c r="H115" s="26" t="n"/>
+      <c r="I115" s="26" t="n"/>
+      <c r="J115" s="27" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -15634,14 +15642,14 @@
           <t>IM(x5,x4) =</t>
         </is>
       </c>
-      <c r="B123" s="10" t="n"/>
-      <c r="C123" s="10" t="n"/>
-      <c r="D123" s="10" t="n"/>
-      <c r="E123" s="10" t="n"/>
-      <c r="F123" s="10" t="n"/>
-      <c r="G123" s="10" t="n"/>
-      <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="n"/>
+      <c r="B123" s="26" t="n"/>
+      <c r="C123" s="26" t="n"/>
+      <c r="D123" s="26" t="n"/>
+      <c r="E123" s="26" t="n"/>
+      <c r="F123" s="26" t="n"/>
+      <c r="G123" s="26" t="n"/>
+      <c r="H123" s="26" t="n"/>
+      <c r="I123" s="27" t="n"/>
       <c r="J123" s="11">
         <f>SUM(J117:J122)</f>
         <v/>
@@ -15653,15 +15661,15 @@
           <t>x5 — x6</t>
         </is>
       </c>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="5" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n"/>
-      <c r="I126" s="5" t="n"/>
-      <c r="J126" s="5" t="n"/>
+      <c r="B126" s="26" t="n"/>
+      <c r="C126" s="26" t="n"/>
+      <c r="D126" s="26" t="n"/>
+      <c r="E126" s="26" t="n"/>
+      <c r="F126" s="26" t="n"/>
+      <c r="G126" s="26" t="n"/>
+      <c r="H126" s="26" t="n"/>
+      <c r="I126" s="26" t="n"/>
+      <c r="J126" s="27" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -15961,14 +15969,14 @@
           <t>IM(x5,x6) =</t>
         </is>
       </c>
-      <c r="B134" s="10" t="n"/>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="10" t="n"/>
-      <c r="E134" s="10" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="10" t="n"/>
-      <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
+      <c r="B134" s="26" t="n"/>
+      <c r="C134" s="26" t="n"/>
+      <c r="D134" s="26" t="n"/>
+      <c r="E134" s="26" t="n"/>
+      <c r="F134" s="26" t="n"/>
+      <c r="G134" s="26" t="n"/>
+      <c r="H134" s="26" t="n"/>
+      <c r="I134" s="27" t="n"/>
       <c r="J134" s="11">
         <f>SUM(J128:J133)</f>
         <v/>
@@ -15980,15 +15988,15 @@
           <t>x5 — x9</t>
         </is>
       </c>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="5" t="n"/>
-      <c r="E137" s="5" t="n"/>
-      <c r="F137" s="5" t="n"/>
-      <c r="G137" s="5" t="n"/>
-      <c r="H137" s="5" t="n"/>
-      <c r="I137" s="5" t="n"/>
-      <c r="J137" s="5" t="n"/>
+      <c r="B137" s="26" t="n"/>
+      <c r="C137" s="26" t="n"/>
+      <c r="D137" s="26" t="n"/>
+      <c r="E137" s="26" t="n"/>
+      <c r="F137" s="26" t="n"/>
+      <c r="G137" s="26" t="n"/>
+      <c r="H137" s="26" t="n"/>
+      <c r="I137" s="26" t="n"/>
+      <c r="J137" s="27" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -16528,14 +16536,14 @@
           <t>IM(x5,x9) =</t>
         </is>
       </c>
-      <c r="B151" s="10" t="n"/>
-      <c r="C151" s="10" t="n"/>
-      <c r="D151" s="10" t="n"/>
-      <c r="E151" s="10" t="n"/>
-      <c r="F151" s="10" t="n"/>
-      <c r="G151" s="10" t="n"/>
-      <c r="H151" s="10" t="n"/>
-      <c r="I151" s="10" t="n"/>
+      <c r="B151" s="26" t="n"/>
+      <c r="C151" s="26" t="n"/>
+      <c r="D151" s="26" t="n"/>
+      <c r="E151" s="26" t="n"/>
+      <c r="F151" s="26" t="n"/>
+      <c r="G151" s="26" t="n"/>
+      <c r="H151" s="26" t="n"/>
+      <c r="I151" s="27" t="n"/>
       <c r="J151" s="11">
         <f>SUM(J139:J150)</f>
         <v/>
@@ -16547,15 +16555,15 @@
           <t>x5 — x3</t>
         </is>
       </c>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5" t="n"/>
-      <c r="H154" s="5" t="n"/>
-      <c r="I154" s="5" t="n"/>
-      <c r="J154" s="5" t="n"/>
+      <c r="B154" s="26" t="n"/>
+      <c r="C154" s="26" t="n"/>
+      <c r="D154" s="26" t="n"/>
+      <c r="E154" s="26" t="n"/>
+      <c r="F154" s="26" t="n"/>
+      <c r="G154" s="26" t="n"/>
+      <c r="H154" s="26" t="n"/>
+      <c r="I154" s="26" t="n"/>
+      <c r="J154" s="27" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -16855,14 +16863,14 @@
           <t>IM(x5,x3) =</t>
         </is>
       </c>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="10" t="n"/>
-      <c r="D162" s="10" t="n"/>
-      <c r="E162" s="10" t="n"/>
-      <c r="F162" s="10" t="n"/>
-      <c r="G162" s="10" t="n"/>
-      <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
+      <c r="B162" s="26" t="n"/>
+      <c r="C162" s="26" t="n"/>
+      <c r="D162" s="26" t="n"/>
+      <c r="E162" s="26" t="n"/>
+      <c r="F162" s="26" t="n"/>
+      <c r="G162" s="26" t="n"/>
+      <c r="H162" s="26" t="n"/>
+      <c r="I162" s="27" t="n"/>
       <c r="J162" s="11">
         <f>SUM(J156:J161)</f>
         <v/>
@@ -16874,15 +16882,15 @@
           <t>x4 — x6</t>
         </is>
       </c>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="5" t="n"/>
-      <c r="D165" s="5" t="n"/>
-      <c r="E165" s="5" t="n"/>
-      <c r="F165" s="5" t="n"/>
-      <c r="G165" s="5" t="n"/>
-      <c r="H165" s="5" t="n"/>
-      <c r="I165" s="5" t="n"/>
-      <c r="J165" s="5" t="n"/>
+      <c r="B165" s="26" t="n"/>
+      <c r="C165" s="26" t="n"/>
+      <c r="D165" s="26" t="n"/>
+      <c r="E165" s="26" t="n"/>
+      <c r="F165" s="26" t="n"/>
+      <c r="G165" s="26" t="n"/>
+      <c r="H165" s="26" t="n"/>
+      <c r="I165" s="26" t="n"/>
+      <c r="J165" s="27" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -17102,14 +17110,14 @@
           <t>IM(x4,x6) =</t>
         </is>
       </c>
-      <c r="B171" s="10" t="n"/>
-      <c r="C171" s="10" t="n"/>
-      <c r="D171" s="10" t="n"/>
-      <c r="E171" s="10" t="n"/>
-      <c r="F171" s="10" t="n"/>
-      <c r="G171" s="10" t="n"/>
-      <c r="H171" s="10" t="n"/>
-      <c r="I171" s="10" t="n"/>
+      <c r="B171" s="26" t="n"/>
+      <c r="C171" s="26" t="n"/>
+      <c r="D171" s="26" t="n"/>
+      <c r="E171" s="26" t="n"/>
+      <c r="F171" s="26" t="n"/>
+      <c r="G171" s="26" t="n"/>
+      <c r="H171" s="26" t="n"/>
+      <c r="I171" s="27" t="n"/>
       <c r="J171" s="11">
         <f>SUM(J167:J170)</f>
         <v/>
@@ -17121,15 +17129,15 @@
           <t>x4 — x9</t>
         </is>
       </c>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="5" t="n"/>
-      <c r="E174" s="5" t="n"/>
-      <c r="F174" s="5" t="n"/>
-      <c r="G174" s="5" t="n"/>
-      <c r="H174" s="5" t="n"/>
-      <c r="I174" s="5" t="n"/>
-      <c r="J174" s="5" t="n"/>
+      <c r="B174" s="26" t="n"/>
+      <c r="C174" s="26" t="n"/>
+      <c r="D174" s="26" t="n"/>
+      <c r="E174" s="26" t="n"/>
+      <c r="F174" s="26" t="n"/>
+      <c r="G174" s="26" t="n"/>
+      <c r="H174" s="26" t="n"/>
+      <c r="I174" s="26" t="n"/>
+      <c r="J174" s="27" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -17509,14 +17517,14 @@
           <t>IM(x4,x9) =</t>
         </is>
       </c>
-      <c r="B184" s="10" t="n"/>
-      <c r="C184" s="10" t="n"/>
-      <c r="D184" s="10" t="n"/>
-      <c r="E184" s="10" t="n"/>
-      <c r="F184" s="10" t="n"/>
-      <c r="G184" s="10" t="n"/>
-      <c r="H184" s="10" t="n"/>
-      <c r="I184" s="10" t="n"/>
+      <c r="B184" s="26" t="n"/>
+      <c r="C184" s="26" t="n"/>
+      <c r="D184" s="26" t="n"/>
+      <c r="E184" s="26" t="n"/>
+      <c r="F184" s="26" t="n"/>
+      <c r="G184" s="26" t="n"/>
+      <c r="H184" s="26" t="n"/>
+      <c r="I184" s="27" t="n"/>
       <c r="J184" s="11">
         <f>SUM(J176:J183)</f>
         <v/>
@@ -17528,15 +17536,15 @@
           <t>x4 — x3</t>
         </is>
       </c>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="5" t="n"/>
-      <c r="F187" s="5" t="n"/>
-      <c r="G187" s="5" t="n"/>
-      <c r="H187" s="5" t="n"/>
-      <c r="I187" s="5" t="n"/>
-      <c r="J187" s="5" t="n"/>
+      <c r="B187" s="26" t="n"/>
+      <c r="C187" s="26" t="n"/>
+      <c r="D187" s="26" t="n"/>
+      <c r="E187" s="26" t="n"/>
+      <c r="F187" s="26" t="n"/>
+      <c r="G187" s="26" t="n"/>
+      <c r="H187" s="26" t="n"/>
+      <c r="I187" s="26" t="n"/>
+      <c r="J187" s="27" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -17756,14 +17764,14 @@
           <t>IM(x4,x3) =</t>
         </is>
       </c>
-      <c r="B193" s="10" t="n"/>
-      <c r="C193" s="10" t="n"/>
-      <c r="D193" s="10" t="n"/>
-      <c r="E193" s="10" t="n"/>
-      <c r="F193" s="10" t="n"/>
-      <c r="G193" s="10" t="n"/>
-      <c r="H193" s="10" t="n"/>
-      <c r="I193" s="10" t="n"/>
+      <c r="B193" s="26" t="n"/>
+      <c r="C193" s="26" t="n"/>
+      <c r="D193" s="26" t="n"/>
+      <c r="E193" s="26" t="n"/>
+      <c r="F193" s="26" t="n"/>
+      <c r="G193" s="26" t="n"/>
+      <c r="H193" s="26" t="n"/>
+      <c r="I193" s="27" t="n"/>
       <c r="J193" s="11">
         <f>SUM(J189:J192)</f>
         <v/>
@@ -17775,15 +17783,15 @@
           <t>x6 — x9</t>
         </is>
       </c>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
-      <c r="E196" s="5" t="n"/>
-      <c r="F196" s="5" t="n"/>
-      <c r="G196" s="5" t="n"/>
-      <c r="H196" s="5" t="n"/>
-      <c r="I196" s="5" t="n"/>
-      <c r="J196" s="5" t="n"/>
+      <c r="B196" s="26" t="n"/>
+      <c r="C196" s="26" t="n"/>
+      <c r="D196" s="26" t="n"/>
+      <c r="E196" s="26" t="n"/>
+      <c r="F196" s="26" t="n"/>
+      <c r="G196" s="26" t="n"/>
+      <c r="H196" s="26" t="n"/>
+      <c r="I196" s="26" t="n"/>
+      <c r="J196" s="27" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -18163,14 +18171,14 @@
           <t>IM(x6,x9) =</t>
         </is>
       </c>
-      <c r="B206" s="10" t="n"/>
-      <c r="C206" s="10" t="n"/>
-      <c r="D206" s="10" t="n"/>
-      <c r="E206" s="10" t="n"/>
-      <c r="F206" s="10" t="n"/>
-      <c r="G206" s="10" t="n"/>
-      <c r="H206" s="10" t="n"/>
-      <c r="I206" s="10" t="n"/>
+      <c r="B206" s="26" t="n"/>
+      <c r="C206" s="26" t="n"/>
+      <c r="D206" s="26" t="n"/>
+      <c r="E206" s="26" t="n"/>
+      <c r="F206" s="26" t="n"/>
+      <c r="G206" s="26" t="n"/>
+      <c r="H206" s="26" t="n"/>
+      <c r="I206" s="27" t="n"/>
       <c r="J206" s="11">
         <f>SUM(J198:J205)</f>
         <v/>
@@ -18182,15 +18190,15 @@
           <t>x6 — x3</t>
         </is>
       </c>
-      <c r="B209" s="5" t="n"/>
-      <c r="C209" s="5" t="n"/>
-      <c r="D209" s="5" t="n"/>
-      <c r="E209" s="5" t="n"/>
-      <c r="F209" s="5" t="n"/>
-      <c r="G209" s="5" t="n"/>
-      <c r="H209" s="5" t="n"/>
-      <c r="I209" s="5" t="n"/>
-      <c r="J209" s="5" t="n"/>
+      <c r="B209" s="26" t="n"/>
+      <c r="C209" s="26" t="n"/>
+      <c r="D209" s="26" t="n"/>
+      <c r="E209" s="26" t="n"/>
+      <c r="F209" s="26" t="n"/>
+      <c r="G209" s="26" t="n"/>
+      <c r="H209" s="26" t="n"/>
+      <c r="I209" s="26" t="n"/>
+      <c r="J209" s="27" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -18410,14 +18418,14 @@
           <t>IM(x6,x3) =</t>
         </is>
       </c>
-      <c r="B215" s="10" t="n"/>
-      <c r="C215" s="10" t="n"/>
-      <c r="D215" s="10" t="n"/>
-      <c r="E215" s="10" t="n"/>
-      <c r="F215" s="10" t="n"/>
-      <c r="G215" s="10" t="n"/>
-      <c r="H215" s="10" t="n"/>
-      <c r="I215" s="10" t="n"/>
+      <c r="B215" s="26" t="n"/>
+      <c r="C215" s="26" t="n"/>
+      <c r="D215" s="26" t="n"/>
+      <c r="E215" s="26" t="n"/>
+      <c r="F215" s="26" t="n"/>
+      <c r="G215" s="26" t="n"/>
+      <c r="H215" s="26" t="n"/>
+      <c r="I215" s="27" t="n"/>
       <c r="J215" s="11">
         <f>SUM(J211:J214)</f>
         <v/>
@@ -18429,15 +18437,15 @@
           <t>x9 — x3</t>
         </is>
       </c>
-      <c r="B218" s="5" t="n"/>
-      <c r="C218" s="5" t="n"/>
-      <c r="D218" s="5" t="n"/>
-      <c r="E218" s="5" t="n"/>
-      <c r="F218" s="5" t="n"/>
-      <c r="G218" s="5" t="n"/>
-      <c r="H218" s="5" t="n"/>
-      <c r="I218" s="5" t="n"/>
-      <c r="J218" s="5" t="n"/>
+      <c r="B218" s="26" t="n"/>
+      <c r="C218" s="26" t="n"/>
+      <c r="D218" s="26" t="n"/>
+      <c r="E218" s="26" t="n"/>
+      <c r="F218" s="26" t="n"/>
+      <c r="G218" s="26" t="n"/>
+      <c r="H218" s="26" t="n"/>
+      <c r="I218" s="26" t="n"/>
+      <c r="J218" s="27" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -18817,14 +18825,14 @@
           <t>IM(x9,x3) =</t>
         </is>
       </c>
-      <c r="B228" s="10" t="n"/>
-      <c r="C228" s="10" t="n"/>
-      <c r="D228" s="10" t="n"/>
-      <c r="E228" s="10" t="n"/>
-      <c r="F228" s="10" t="n"/>
-      <c r="G228" s="10" t="n"/>
-      <c r="H228" s="10" t="n"/>
-      <c r="I228" s="10" t="n"/>
+      <c r="B228" s="26" t="n"/>
+      <c r="C228" s="26" t="n"/>
+      <c r="D228" s="26" t="n"/>
+      <c r="E228" s="26" t="n"/>
+      <c r="F228" s="26" t="n"/>
+      <c r="G228" s="26" t="n"/>
+      <c r="H228" s="26" t="n"/>
+      <c r="I228" s="27" t="n"/>
       <c r="J228" s="11">
         <f>SUM(J220:J227)</f>
         <v/>
@@ -18834,8 +18842,8 @@
   <mergeCells count="42">
     <mergeCell ref="A90:I90"/>
     <mergeCell ref="A126:J126"/>
+    <mergeCell ref="A193:I193"/>
     <mergeCell ref="A106:J106"/>
-    <mergeCell ref="A193:I193"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A209:J209"/>
     <mergeCell ref="A165:J165"/>
@@ -18910,18 +18918,17 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H(x1)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -19015,19 +19022,17 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>H(x2)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -19121,19 +19126,17 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>H(x5)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -19248,19 +19251,17 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
           <t>H(x4)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -19354,19 +19355,17 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>H(x6)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -19460,19 +19459,17 @@
         <v/>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
           <t>H(x9)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="27" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -19608,19 +19605,17 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>H(x3)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="27" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -19756,7 +19751,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -20072,7 +20066,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -20080,7 +20073,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -20350,9 +20342,9 @@
           <t>IM(x1,x5) = Σ</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="27" t="n"/>
       <c r="I12" s="11">
         <f>SUM(I6:I11)</f>
         <v/>
@@ -21842,7 +21834,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -22043,17 +22034,16 @@
         <v>2.8337</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>PESO TOTAL MST (Prim)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="27" t="n"/>
       <c r="F11" s="11" t="n">
         <v>2.8337</v>
       </c>
@@ -22089,7 +22079,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -22208,14 +22197,13 @@
         <v>2.8337</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>PESO TOTAL MST</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
+      <c r="B11" s="27" t="n"/>
       <c r="C11" s="11" t="n">
         <v>2.8337</v>
       </c>
@@ -22225,6 +22213,882 @@
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A11:B11"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Matriz de Distancias de Caminos - Dataset A (x7=0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>d(i,j)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Suma fila</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1.1106</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1.1166</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>1.4304</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="I4" s="11">
+        <f>SUM(B4:H4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1.1106</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.6996</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1.3798</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0.6869</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1.6936</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="I5" s="11">
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>0.6996</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1.0056</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="I6" s="11">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1.1166</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1.3798</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.6918</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>1.6858</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="I7" s="11">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.6869</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.6929</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1.0067</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="I8" s="11">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1.4304</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1.6936</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.0056</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1.6858</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1.0067</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="I9" s="11">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0.6938</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.0069</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.9998</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Matriz de Distancias de Caminos - Dataset B (x7=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>d(i,j)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
+        <is>
+          <t>Suma fila</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1.0705</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>1.1787</v>
+      </c>
+      <c r="F4" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G4" s="9" t="n">
+        <v>1.4286</v>
+      </c>
+      <c r="H4" s="9" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="I4" s="11">
+        <f>SUM(B4:H4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>1.0705</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1.4192</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1.6691</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="I5" s="11">
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1.0727</v>
+      </c>
+      <c r="D6" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1.1809</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>1.4308</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="I6" s="11">
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1.1787</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1.4192</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1.1809</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.7637</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>1.7449</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+      <c r="I7" s="11">
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>0.6555</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.7637</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>1.0136</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="I8" s="11">
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1.4286</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1.6691</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>1.4308</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1.7449</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1.0136</v>
+      </c>
+      <c r="G9" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="I9" s="11">
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>0.4312</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>0.6717</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.4334</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.7475000000000001</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.9974</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="11">
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="inlineStr">
+        <is>
+          <t>Analisis de Sensibilidad - Metodo rVP (Rango de Variacion Permitido)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>D = Suma_A - Suma_B  |  Variable critica si |D| &gt; 0.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Variable</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Suma_A (Dataset A)</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Suma_B (Dataset B)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>D = Suma_A - Suma_B</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>|D|</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Critica?</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>x1</t>
+        </is>
+      </c>
+      <c r="B5" s="19">
+        <f>'Rutas MST A'!I4</f>
+        <v/>
+      </c>
+      <c r="C5" s="19">
+        <f>'Rutas MST B'!I4</f>
+        <v/>
+      </c>
+      <c r="D5" s="11">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="19">
+        <f>ABS(D5)</f>
+        <v/>
+      </c>
+      <c r="F5" s="20">
+        <f>IF(E5&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>x2</t>
+        </is>
+      </c>
+      <c r="B6" s="19">
+        <f>'Rutas MST A'!I5</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>'Rutas MST B'!I5</f>
+        <v/>
+      </c>
+      <c r="D6" s="11">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="19">
+        <f>ABS(D6)</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>IF(E6&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>x3</t>
+        </is>
+      </c>
+      <c r="B7" s="23">
+        <f>'Rutas MST A'!I6</f>
+        <v/>
+      </c>
+      <c r="C7" s="23">
+        <f>'Rutas MST B'!I6</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="23">
+        <f>ABS(D7)</f>
+        <v/>
+      </c>
+      <c r="F7" s="24">
+        <f>IF(E7&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>x4</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
+        <f>'Rutas MST A'!I7</f>
+        <v/>
+      </c>
+      <c r="C8" s="23">
+        <f>'Rutas MST B'!I7</f>
+        <v/>
+      </c>
+      <c r="D8" s="28">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="23">
+        <f>ABS(D8)</f>
+        <v/>
+      </c>
+      <c r="F8" s="24">
+        <f>IF(E8&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>x5</t>
+        </is>
+      </c>
+      <c r="B9" s="19">
+        <f>'Rutas MST A'!I8</f>
+        <v/>
+      </c>
+      <c r="C9" s="19">
+        <f>'Rutas MST B'!I8</f>
+        <v/>
+      </c>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="19">
+        <f>ABS(D9)</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>IF(E9&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>x6</t>
+        </is>
+      </c>
+      <c r="B10" s="19">
+        <f>'Rutas MST A'!I9</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>'Rutas MST B'!I9</f>
+        <v/>
+      </c>
+      <c r="D10" s="11">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="19">
+        <f>ABS(D10)</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>IF(E10&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>x9</t>
+        </is>
+      </c>
+      <c r="B11" s="19">
+        <f>'Rutas MST A'!I10</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>'Rutas MST B'!I10</f>
+        <v/>
+      </c>
+      <c r="D11" s="11">
+        <f>B11-C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="19">
+        <f>ABS(D11)</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>IF(E11&gt;0.5,"Si","No")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22262,15 +23126,15 @@
           <t>x1 — x2</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
-      <c r="I4" s="5" t="n"/>
-      <c r="J4" s="5" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="26" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -22490,14 +23354,14 @@
           <t>IM(x1,x2) =</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="10" t="n"/>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="26" t="n"/>
+      <c r="I10" s="27" t="n"/>
       <c r="J10" s="11">
         <f>SUM(J6:J9)</f>
         <v/>
@@ -22509,15 +23373,15 @@
           <t>x1 — x5</t>
         </is>
       </c>
-      <c r="B13" s="5" t="n"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
-      <c r="H13" s="5" t="n"/>
-      <c r="I13" s="5" t="n"/>
-      <c r="J13" s="5" t="n"/>
+      <c r="B13" s="26" t="n"/>
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="26" t="n"/>
+      <c r="E13" s="26" t="n"/>
+      <c r="F13" s="26" t="n"/>
+      <c r="G13" s="26" t="n"/>
+      <c r="H13" s="26" t="n"/>
+      <c r="I13" s="26" t="n"/>
+      <c r="J13" s="27" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -22817,14 +23681,14 @@
           <t>IM(x1,x5) =</t>
         </is>
       </c>
-      <c r="B21" s="10" t="n"/>
-      <c r="C21" s="10" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="10" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
+      <c r="B21" s="26" t="n"/>
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="26" t="n"/>
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
+      <c r="H21" s="26" t="n"/>
+      <c r="I21" s="27" t="n"/>
       <c r="J21" s="11">
         <f>SUM(J15:J20)</f>
         <v/>
@@ -22836,15 +23700,15 @@
           <t>x1 — x4</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
-      <c r="H24" s="5" t="n"/>
-      <c r="I24" s="5" t="n"/>
-      <c r="J24" s="5" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="26" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="27" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -23064,14 +23928,14 @@
           <t>IM(x1,x4) =</t>
         </is>
       </c>
-      <c r="B30" s="10" t="n"/>
-      <c r="C30" s="10" t="n"/>
-      <c r="D30" s="10" t="n"/>
-      <c r="E30" s="10" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="26" t="n"/>
+      <c r="I30" s="27" t="n"/>
       <c r="J30" s="11">
         <f>SUM(J26:J29)</f>
         <v/>
@@ -23083,15 +23947,15 @@
           <t>x1 — x6</t>
         </is>
       </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
-      <c r="H33" s="5" t="n"/>
-      <c r="I33" s="5" t="n"/>
-      <c r="J33" s="5" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="n"/>
+      <c r="H33" s="26" t="n"/>
+      <c r="I33" s="26" t="n"/>
+      <c r="J33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -23311,14 +24175,14 @@
           <t>IM(x1,x6) =</t>
         </is>
       </c>
-      <c r="B39" s="10" t="n"/>
-      <c r="C39" s="10" t="n"/>
-      <c r="D39" s="10" t="n"/>
-      <c r="E39" s="10" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="10" t="n"/>
-      <c r="H39" s="10" t="n"/>
-      <c r="I39" s="10" t="n"/>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+      <c r="E39" s="26" t="n"/>
+      <c r="F39" s="26" t="n"/>
+      <c r="G39" s="26" t="n"/>
+      <c r="H39" s="26" t="n"/>
+      <c r="I39" s="27" t="n"/>
       <c r="J39" s="11">
         <f>SUM(J35:J38)</f>
         <v/>
@@ -23330,15 +24194,15 @@
           <t>x1 — x9</t>
         </is>
       </c>
-      <c r="B42" s="5" t="n"/>
-      <c r="C42" s="5" t="n"/>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
-      <c r="H42" s="5" t="n"/>
-      <c r="I42" s="5" t="n"/>
-      <c r="J42" s="5" t="n"/>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
+      <c r="F42" s="26" t="n"/>
+      <c r="G42" s="26" t="n"/>
+      <c r="H42" s="26" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="27" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -23718,14 +24582,14 @@
           <t>IM(x1,x9) =</t>
         </is>
       </c>
-      <c r="B52" s="10" t="n"/>
-      <c r="C52" s="10" t="n"/>
-      <c r="D52" s="10" t="n"/>
-      <c r="E52" s="10" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="10" t="n"/>
-      <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
+      <c r="B52" s="26" t="n"/>
+      <c r="C52" s="26" t="n"/>
+      <c r="D52" s="26" t="n"/>
+      <c r="E52" s="26" t="n"/>
+      <c r="F52" s="26" t="n"/>
+      <c r="G52" s="26" t="n"/>
+      <c r="H52" s="26" t="n"/>
+      <c r="I52" s="27" t="n"/>
       <c r="J52" s="11">
         <f>SUM(J44:J51)</f>
         <v/>
@@ -23737,15 +24601,15 @@
           <t>x1 — x3</t>
         </is>
       </c>
-      <c r="B55" s="5" t="n"/>
-      <c r="C55" s="5" t="n"/>
-      <c r="D55" s="5" t="n"/>
-      <c r="E55" s="5" t="n"/>
-      <c r="F55" s="5" t="n"/>
-      <c r="G55" s="5" t="n"/>
-      <c r="H55" s="5" t="n"/>
-      <c r="I55" s="5" t="n"/>
-      <c r="J55" s="5" t="n"/>
+      <c r="B55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="26" t="n"/>
+      <c r="E55" s="26" t="n"/>
+      <c r="F55" s="26" t="n"/>
+      <c r="G55" s="26" t="n"/>
+      <c r="H55" s="26" t="n"/>
+      <c r="I55" s="26" t="n"/>
+      <c r="J55" s="27" t="n"/>
     </row>
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
@@ -23965,14 +24829,14 @@
           <t>IM(x1,x3) =</t>
         </is>
       </c>
-      <c r="B61" s="10" t="n"/>
-      <c r="C61" s="10" t="n"/>
-      <c r="D61" s="10" t="n"/>
-      <c r="E61" s="10" t="n"/>
-      <c r="F61" s="10" t="n"/>
-      <c r="G61" s="10" t="n"/>
-      <c r="H61" s="10" t="n"/>
-      <c r="I61" s="10" t="n"/>
+      <c r="B61" s="26" t="n"/>
+      <c r="C61" s="26" t="n"/>
+      <c r="D61" s="26" t="n"/>
+      <c r="E61" s="26" t="n"/>
+      <c r="F61" s="26" t="n"/>
+      <c r="G61" s="26" t="n"/>
+      <c r="H61" s="26" t="n"/>
+      <c r="I61" s="27" t="n"/>
       <c r="J61" s="11">
         <f>SUM(J57:J60)</f>
         <v/>
@@ -23984,15 +24848,15 @@
           <t>x2 — x5</t>
         </is>
       </c>
-      <c r="B64" s="5" t="n"/>
-      <c r="C64" s="5" t="n"/>
-      <c r="D64" s="5" t="n"/>
-      <c r="E64" s="5" t="n"/>
-      <c r="F64" s="5" t="n"/>
-      <c r="G64" s="5" t="n"/>
-      <c r="H64" s="5" t="n"/>
-      <c r="I64" s="5" t="n"/>
-      <c r="J64" s="5" t="n"/>
+      <c r="B64" s="26" t="n"/>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="26" t="n"/>
+      <c r="E64" s="26" t="n"/>
+      <c r="F64" s="26" t="n"/>
+      <c r="G64" s="26" t="n"/>
+      <c r="H64" s="26" t="n"/>
+      <c r="I64" s="26" t="n"/>
+      <c r="J64" s="27" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
@@ -24292,14 +25156,14 @@
           <t>IM(x2,x5) =</t>
         </is>
       </c>
-      <c r="B72" s="10" t="n"/>
-      <c r="C72" s="10" t="n"/>
-      <c r="D72" s="10" t="n"/>
-      <c r="E72" s="10" t="n"/>
-      <c r="F72" s="10" t="n"/>
-      <c r="G72" s="10" t="n"/>
-      <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
+      <c r="B72" s="26" t="n"/>
+      <c r="C72" s="26" t="n"/>
+      <c r="D72" s="26" t="n"/>
+      <c r="E72" s="26" t="n"/>
+      <c r="F72" s="26" t="n"/>
+      <c r="G72" s="26" t="n"/>
+      <c r="H72" s="26" t="n"/>
+      <c r="I72" s="27" t="n"/>
       <c r="J72" s="11">
         <f>SUM(J66:J71)</f>
         <v/>
@@ -24311,15 +25175,15 @@
           <t>x2 — x4</t>
         </is>
       </c>
-      <c r="B75" s="5" t="n"/>
-      <c r="C75" s="5" t="n"/>
-      <c r="D75" s="5" t="n"/>
-      <c r="E75" s="5" t="n"/>
-      <c r="F75" s="5" t="n"/>
-      <c r="G75" s="5" t="n"/>
-      <c r="H75" s="5" t="n"/>
-      <c r="I75" s="5" t="n"/>
-      <c r="J75" s="5" t="n"/>
+      <c r="B75" s="26" t="n"/>
+      <c r="C75" s="26" t="n"/>
+      <c r="D75" s="26" t="n"/>
+      <c r="E75" s="26" t="n"/>
+      <c r="F75" s="26" t="n"/>
+      <c r="G75" s="26" t="n"/>
+      <c r="H75" s="26" t="n"/>
+      <c r="I75" s="26" t="n"/>
+      <c r="J75" s="27" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
@@ -24539,14 +25403,14 @@
           <t>IM(x2,x4) =</t>
         </is>
       </c>
-      <c r="B81" s="10" t="n"/>
-      <c r="C81" s="10" t="n"/>
-      <c r="D81" s="10" t="n"/>
-      <c r="E81" s="10" t="n"/>
-      <c r="F81" s="10" t="n"/>
-      <c r="G81" s="10" t="n"/>
-      <c r="H81" s="10" t="n"/>
-      <c r="I81" s="10" t="n"/>
+      <c r="B81" s="26" t="n"/>
+      <c r="C81" s="26" t="n"/>
+      <c r="D81" s="26" t="n"/>
+      <c r="E81" s="26" t="n"/>
+      <c r="F81" s="26" t="n"/>
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="26" t="n"/>
+      <c r="I81" s="27" t="n"/>
       <c r="J81" s="11">
         <f>SUM(J77:J80)</f>
         <v/>
@@ -24558,15 +25422,15 @@
           <t>x2 — x6</t>
         </is>
       </c>
-      <c r="B84" s="5" t="n"/>
-      <c r="C84" s="5" t="n"/>
-      <c r="D84" s="5" t="n"/>
-      <c r="E84" s="5" t="n"/>
-      <c r="F84" s="5" t="n"/>
-      <c r="G84" s="5" t="n"/>
-      <c r="H84" s="5" t="n"/>
-      <c r="I84" s="5" t="n"/>
-      <c r="J84" s="5" t="n"/>
+      <c r="B84" s="26" t="n"/>
+      <c r="C84" s="26" t="n"/>
+      <c r="D84" s="26" t="n"/>
+      <c r="E84" s="26" t="n"/>
+      <c r="F84" s="26" t="n"/>
+      <c r="G84" s="26" t="n"/>
+      <c r="H84" s="26" t="n"/>
+      <c r="I84" s="26" t="n"/>
+      <c r="J84" s="27" t="n"/>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
@@ -24786,14 +25650,14 @@
           <t>IM(x2,x6) =</t>
         </is>
       </c>
-      <c r="B90" s="10" t="n"/>
-      <c r="C90" s="10" t="n"/>
-      <c r="D90" s="10" t="n"/>
-      <c r="E90" s="10" t="n"/>
-      <c r="F90" s="10" t="n"/>
-      <c r="G90" s="10" t="n"/>
-      <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
+      <c r="B90" s="26" t="n"/>
+      <c r="C90" s="26" t="n"/>
+      <c r="D90" s="26" t="n"/>
+      <c r="E90" s="26" t="n"/>
+      <c r="F90" s="26" t="n"/>
+      <c r="G90" s="26" t="n"/>
+      <c r="H90" s="26" t="n"/>
+      <c r="I90" s="27" t="n"/>
       <c r="J90" s="11">
         <f>SUM(J86:J89)</f>
         <v/>
@@ -24805,15 +25669,15 @@
           <t>x2 — x9</t>
         </is>
       </c>
-      <c r="B93" s="5" t="n"/>
-      <c r="C93" s="5" t="n"/>
-      <c r="D93" s="5" t="n"/>
-      <c r="E93" s="5" t="n"/>
-      <c r="F93" s="5" t="n"/>
-      <c r="G93" s="5" t="n"/>
-      <c r="H93" s="5" t="n"/>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="5" t="n"/>
+      <c r="B93" s="26" t="n"/>
+      <c r="C93" s="26" t="n"/>
+      <c r="D93" s="26" t="n"/>
+      <c r="E93" s="26" t="n"/>
+      <c r="F93" s="26" t="n"/>
+      <c r="G93" s="26" t="n"/>
+      <c r="H93" s="26" t="n"/>
+      <c r="I93" s="26" t="n"/>
+      <c r="J93" s="27" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
@@ -25193,14 +26057,14 @@
           <t>IM(x2,x9) =</t>
         </is>
       </c>
-      <c r="B103" s="10" t="n"/>
-      <c r="C103" s="10" t="n"/>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="10" t="n"/>
-      <c r="F103" s="10" t="n"/>
-      <c r="G103" s="10" t="n"/>
-      <c r="H103" s="10" t="n"/>
-      <c r="I103" s="10" t="n"/>
+      <c r="B103" s="26" t="n"/>
+      <c r="C103" s="26" t="n"/>
+      <c r="D103" s="26" t="n"/>
+      <c r="E103" s="26" t="n"/>
+      <c r="F103" s="26" t="n"/>
+      <c r="G103" s="26" t="n"/>
+      <c r="H103" s="26" t="n"/>
+      <c r="I103" s="27" t="n"/>
       <c r="J103" s="11">
         <f>SUM(J95:J102)</f>
         <v/>
@@ -25212,15 +26076,15 @@
           <t>x2 — x3</t>
         </is>
       </c>
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="F106" s="5" t="n"/>
-      <c r="G106" s="5" t="n"/>
-      <c r="H106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
-      <c r="J106" s="5" t="n"/>
+      <c r="B106" s="26" t="n"/>
+      <c r="C106" s="26" t="n"/>
+      <c r="D106" s="26" t="n"/>
+      <c r="E106" s="26" t="n"/>
+      <c r="F106" s="26" t="n"/>
+      <c r="G106" s="26" t="n"/>
+      <c r="H106" s="26" t="n"/>
+      <c r="I106" s="26" t="n"/>
+      <c r="J106" s="27" t="n"/>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
@@ -25440,14 +26304,14 @@
           <t>IM(x2,x3) =</t>
         </is>
       </c>
-      <c r="B112" s="10" t="n"/>
-      <c r="C112" s="10" t="n"/>
-      <c r="D112" s="10" t="n"/>
-      <c r="E112" s="10" t="n"/>
-      <c r="F112" s="10" t="n"/>
-      <c r="G112" s="10" t="n"/>
-      <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
+      <c r="B112" s="26" t="n"/>
+      <c r="C112" s="26" t="n"/>
+      <c r="D112" s="26" t="n"/>
+      <c r="E112" s="26" t="n"/>
+      <c r="F112" s="26" t="n"/>
+      <c r="G112" s="26" t="n"/>
+      <c r="H112" s="26" t="n"/>
+      <c r="I112" s="27" t="n"/>
       <c r="J112" s="11">
         <f>SUM(J108:J111)</f>
         <v/>
@@ -25459,15 +26323,15 @@
           <t>x5 — x4</t>
         </is>
       </c>
-      <c r="B115" s="5" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="5" t="n"/>
-      <c r="E115" s="5" t="n"/>
-      <c r="F115" s="5" t="n"/>
-      <c r="G115" s="5" t="n"/>
-      <c r="H115" s="5" t="n"/>
-      <c r="I115" s="5" t="n"/>
-      <c r="J115" s="5" t="n"/>
+      <c r="B115" s="26" t="n"/>
+      <c r="C115" s="26" t="n"/>
+      <c r="D115" s="26" t="n"/>
+      <c r="E115" s="26" t="n"/>
+      <c r="F115" s="26" t="n"/>
+      <c r="G115" s="26" t="n"/>
+      <c r="H115" s="26" t="n"/>
+      <c r="I115" s="26" t="n"/>
+      <c r="J115" s="27" t="n"/>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
@@ -25767,14 +26631,14 @@
           <t>IM(x5,x4) =</t>
         </is>
       </c>
-      <c r="B123" s="10" t="n"/>
-      <c r="C123" s="10" t="n"/>
-      <c r="D123" s="10" t="n"/>
-      <c r="E123" s="10" t="n"/>
-      <c r="F123" s="10" t="n"/>
-      <c r="G123" s="10" t="n"/>
-      <c r="H123" s="10" t="n"/>
-      <c r="I123" s="10" t="n"/>
+      <c r="B123" s="26" t="n"/>
+      <c r="C123" s="26" t="n"/>
+      <c r="D123" s="26" t="n"/>
+      <c r="E123" s="26" t="n"/>
+      <c r="F123" s="26" t="n"/>
+      <c r="G123" s="26" t="n"/>
+      <c r="H123" s="26" t="n"/>
+      <c r="I123" s="27" t="n"/>
       <c r="J123" s="11">
         <f>SUM(J117:J122)</f>
         <v/>
@@ -25786,15 +26650,15 @@
           <t>x5 — x6</t>
         </is>
       </c>
-      <c r="B126" s="5" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="5" t="n"/>
-      <c r="E126" s="5" t="n"/>
-      <c r="F126" s="5" t="n"/>
-      <c r="G126" s="5" t="n"/>
-      <c r="H126" s="5" t="n"/>
-      <c r="I126" s="5" t="n"/>
-      <c r="J126" s="5" t="n"/>
+      <c r="B126" s="26" t="n"/>
+      <c r="C126" s="26" t="n"/>
+      <c r="D126" s="26" t="n"/>
+      <c r="E126" s="26" t="n"/>
+      <c r="F126" s="26" t="n"/>
+      <c r="G126" s="26" t="n"/>
+      <c r="H126" s="26" t="n"/>
+      <c r="I126" s="26" t="n"/>
+      <c r="J126" s="27" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
@@ -26094,14 +26958,14 @@
           <t>IM(x5,x6) =</t>
         </is>
       </c>
-      <c r="B134" s="10" t="n"/>
-      <c r="C134" s="10" t="n"/>
-      <c r="D134" s="10" t="n"/>
-      <c r="E134" s="10" t="n"/>
-      <c r="F134" s="10" t="n"/>
-      <c r="G134" s="10" t="n"/>
-      <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
+      <c r="B134" s="26" t="n"/>
+      <c r="C134" s="26" t="n"/>
+      <c r="D134" s="26" t="n"/>
+      <c r="E134" s="26" t="n"/>
+      <c r="F134" s="26" t="n"/>
+      <c r="G134" s="26" t="n"/>
+      <c r="H134" s="26" t="n"/>
+      <c r="I134" s="27" t="n"/>
       <c r="J134" s="11">
         <f>SUM(J128:J133)</f>
         <v/>
@@ -26113,15 +26977,15 @@
           <t>x5 — x9</t>
         </is>
       </c>
-      <c r="B137" s="5" t="n"/>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="5" t="n"/>
-      <c r="E137" s="5" t="n"/>
-      <c r="F137" s="5" t="n"/>
-      <c r="G137" s="5" t="n"/>
-      <c r="H137" s="5" t="n"/>
-      <c r="I137" s="5" t="n"/>
-      <c r="J137" s="5" t="n"/>
+      <c r="B137" s="26" t="n"/>
+      <c r="C137" s="26" t="n"/>
+      <c r="D137" s="26" t="n"/>
+      <c r="E137" s="26" t="n"/>
+      <c r="F137" s="26" t="n"/>
+      <c r="G137" s="26" t="n"/>
+      <c r="H137" s="26" t="n"/>
+      <c r="I137" s="26" t="n"/>
+      <c r="J137" s="27" t="n"/>
     </row>
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
@@ -26661,14 +27525,14 @@
           <t>IM(x5,x9) =</t>
         </is>
       </c>
-      <c r="B151" s="10" t="n"/>
-      <c r="C151" s="10" t="n"/>
-      <c r="D151" s="10" t="n"/>
-      <c r="E151" s="10" t="n"/>
-      <c r="F151" s="10" t="n"/>
-      <c r="G151" s="10" t="n"/>
-      <c r="H151" s="10" t="n"/>
-      <c r="I151" s="10" t="n"/>
+      <c r="B151" s="26" t="n"/>
+      <c r="C151" s="26" t="n"/>
+      <c r="D151" s="26" t="n"/>
+      <c r="E151" s="26" t="n"/>
+      <c r="F151" s="26" t="n"/>
+      <c r="G151" s="26" t="n"/>
+      <c r="H151" s="26" t="n"/>
+      <c r="I151" s="27" t="n"/>
       <c r="J151" s="11">
         <f>SUM(J139:J150)</f>
         <v/>
@@ -26680,15 +27544,15 @@
           <t>x5 — x3</t>
         </is>
       </c>
-      <c r="B154" s="5" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="5" t="n"/>
-      <c r="E154" s="5" t="n"/>
-      <c r="F154" s="5" t="n"/>
-      <c r="G154" s="5" t="n"/>
-      <c r="H154" s="5" t="n"/>
-      <c r="I154" s="5" t="n"/>
-      <c r="J154" s="5" t="n"/>
+      <c r="B154" s="26" t="n"/>
+      <c r="C154" s="26" t="n"/>
+      <c r="D154" s="26" t="n"/>
+      <c r="E154" s="26" t="n"/>
+      <c r="F154" s="26" t="n"/>
+      <c r="G154" s="26" t="n"/>
+      <c r="H154" s="26" t="n"/>
+      <c r="I154" s="26" t="n"/>
+      <c r="J154" s="27" t="n"/>
     </row>
     <row r="155">
       <c r="A155" s="6" t="inlineStr">
@@ -26988,14 +27852,14 @@
           <t>IM(x5,x3) =</t>
         </is>
       </c>
-      <c r="B162" s="10" t="n"/>
-      <c r="C162" s="10" t="n"/>
-      <c r="D162" s="10" t="n"/>
-      <c r="E162" s="10" t="n"/>
-      <c r="F162" s="10" t="n"/>
-      <c r="G162" s="10" t="n"/>
-      <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
+      <c r="B162" s="26" t="n"/>
+      <c r="C162" s="26" t="n"/>
+      <c r="D162" s="26" t="n"/>
+      <c r="E162" s="26" t="n"/>
+      <c r="F162" s="26" t="n"/>
+      <c r="G162" s="26" t="n"/>
+      <c r="H162" s="26" t="n"/>
+      <c r="I162" s="27" t="n"/>
       <c r="J162" s="11">
         <f>SUM(J156:J161)</f>
         <v/>
@@ -27007,15 +27871,15 @@
           <t>x4 — x6</t>
         </is>
       </c>
-      <c r="B165" s="5" t="n"/>
-      <c r="C165" s="5" t="n"/>
-      <c r="D165" s="5" t="n"/>
-      <c r="E165" s="5" t="n"/>
-      <c r="F165" s="5" t="n"/>
-      <c r="G165" s="5" t="n"/>
-      <c r="H165" s="5" t="n"/>
-      <c r="I165" s="5" t="n"/>
-      <c r="J165" s="5" t="n"/>
+      <c r="B165" s="26" t="n"/>
+      <c r="C165" s="26" t="n"/>
+      <c r="D165" s="26" t="n"/>
+      <c r="E165" s="26" t="n"/>
+      <c r="F165" s="26" t="n"/>
+      <c r="G165" s="26" t="n"/>
+      <c r="H165" s="26" t="n"/>
+      <c r="I165" s="26" t="n"/>
+      <c r="J165" s="27" t="n"/>
     </row>
     <row r="166">
       <c r="A166" s="6" t="inlineStr">
@@ -27235,14 +28099,14 @@
           <t>IM(x4,x6) =</t>
         </is>
       </c>
-      <c r="B171" s="10" t="n"/>
-      <c r="C171" s="10" t="n"/>
-      <c r="D171" s="10" t="n"/>
-      <c r="E171" s="10" t="n"/>
-      <c r="F171" s="10" t="n"/>
-      <c r="G171" s="10" t="n"/>
-      <c r="H171" s="10" t="n"/>
-      <c r="I171" s="10" t="n"/>
+      <c r="B171" s="26" t="n"/>
+      <c r="C171" s="26" t="n"/>
+      <c r="D171" s="26" t="n"/>
+      <c r="E171" s="26" t="n"/>
+      <c r="F171" s="26" t="n"/>
+      <c r="G171" s="26" t="n"/>
+      <c r="H171" s="26" t="n"/>
+      <c r="I171" s="27" t="n"/>
       <c r="J171" s="11">
         <f>SUM(J167:J170)</f>
         <v/>
@@ -27254,15 +28118,15 @@
           <t>x4 — x9</t>
         </is>
       </c>
-      <c r="B174" s="5" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="5" t="n"/>
-      <c r="E174" s="5" t="n"/>
-      <c r="F174" s="5" t="n"/>
-      <c r="G174" s="5" t="n"/>
-      <c r="H174" s="5" t="n"/>
-      <c r="I174" s="5" t="n"/>
-      <c r="J174" s="5" t="n"/>
+      <c r="B174" s="26" t="n"/>
+      <c r="C174" s="26" t="n"/>
+      <c r="D174" s="26" t="n"/>
+      <c r="E174" s="26" t="n"/>
+      <c r="F174" s="26" t="n"/>
+      <c r="G174" s="26" t="n"/>
+      <c r="H174" s="26" t="n"/>
+      <c r="I174" s="26" t="n"/>
+      <c r="J174" s="27" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="6" t="inlineStr">
@@ -27642,14 +28506,14 @@
           <t>IM(x4,x9) =</t>
         </is>
       </c>
-      <c r="B184" s="10" t="n"/>
-      <c r="C184" s="10" t="n"/>
-      <c r="D184" s="10" t="n"/>
-      <c r="E184" s="10" t="n"/>
-      <c r="F184" s="10" t="n"/>
-      <c r="G184" s="10" t="n"/>
-      <c r="H184" s="10" t="n"/>
-      <c r="I184" s="10" t="n"/>
+      <c r="B184" s="26" t="n"/>
+      <c r="C184" s="26" t="n"/>
+      <c r="D184" s="26" t="n"/>
+      <c r="E184" s="26" t="n"/>
+      <c r="F184" s="26" t="n"/>
+      <c r="G184" s="26" t="n"/>
+      <c r="H184" s="26" t="n"/>
+      <c r="I184" s="27" t="n"/>
       <c r="J184" s="11">
         <f>SUM(J176:J183)</f>
         <v/>
@@ -27661,15 +28525,15 @@
           <t>x4 — x3</t>
         </is>
       </c>
-      <c r="B187" s="5" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="5" t="n"/>
-      <c r="E187" s="5" t="n"/>
-      <c r="F187" s="5" t="n"/>
-      <c r="G187" s="5" t="n"/>
-      <c r="H187" s="5" t="n"/>
-      <c r="I187" s="5" t="n"/>
-      <c r="J187" s="5" t="n"/>
+      <c r="B187" s="26" t="n"/>
+      <c r="C187" s="26" t="n"/>
+      <c r="D187" s="26" t="n"/>
+      <c r="E187" s="26" t="n"/>
+      <c r="F187" s="26" t="n"/>
+      <c r="G187" s="26" t="n"/>
+      <c r="H187" s="26" t="n"/>
+      <c r="I187" s="26" t="n"/>
+      <c r="J187" s="27" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="6" t="inlineStr">
@@ -27889,14 +28753,14 @@
           <t>IM(x4,x3) =</t>
         </is>
       </c>
-      <c r="B193" s="10" t="n"/>
-      <c r="C193" s="10" t="n"/>
-      <c r="D193" s="10" t="n"/>
-      <c r="E193" s="10" t="n"/>
-      <c r="F193" s="10" t="n"/>
-      <c r="G193" s="10" t="n"/>
-      <c r="H193" s="10" t="n"/>
-      <c r="I193" s="10" t="n"/>
+      <c r="B193" s="26" t="n"/>
+      <c r="C193" s="26" t="n"/>
+      <c r="D193" s="26" t="n"/>
+      <c r="E193" s="26" t="n"/>
+      <c r="F193" s="26" t="n"/>
+      <c r="G193" s="26" t="n"/>
+      <c r="H193" s="26" t="n"/>
+      <c r="I193" s="27" t="n"/>
       <c r="J193" s="11">
         <f>SUM(J189:J192)</f>
         <v/>
@@ -27908,15 +28772,15 @@
           <t>x6 — x9</t>
         </is>
       </c>
-      <c r="B196" s="5" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="5" t="n"/>
-      <c r="E196" s="5" t="n"/>
-      <c r="F196" s="5" t="n"/>
-      <c r="G196" s="5" t="n"/>
-      <c r="H196" s="5" t="n"/>
-      <c r="I196" s="5" t="n"/>
-      <c r="J196" s="5" t="n"/>
+      <c r="B196" s="26" t="n"/>
+      <c r="C196" s="26" t="n"/>
+      <c r="D196" s="26" t="n"/>
+      <c r="E196" s="26" t="n"/>
+      <c r="F196" s="26" t="n"/>
+      <c r="G196" s="26" t="n"/>
+      <c r="H196" s="26" t="n"/>
+      <c r="I196" s="26" t="n"/>
+      <c r="J196" s="27" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="6" t="inlineStr">
@@ -28296,14 +29160,14 @@
           <t>IM(x6,x9) =</t>
         </is>
       </c>
-      <c r="B206" s="10" t="n"/>
-      <c r="C206" s="10" t="n"/>
-      <c r="D206" s="10" t="n"/>
-      <c r="E206" s="10" t="n"/>
-      <c r="F206" s="10" t="n"/>
-      <c r="G206" s="10" t="n"/>
-      <c r="H206" s="10" t="n"/>
-      <c r="I206" s="10" t="n"/>
+      <c r="B206" s="26" t="n"/>
+      <c r="C206" s="26" t="n"/>
+      <c r="D206" s="26" t="n"/>
+      <c r="E206" s="26" t="n"/>
+      <c r="F206" s="26" t="n"/>
+      <c r="G206" s="26" t="n"/>
+      <c r="H206" s="26" t="n"/>
+      <c r="I206" s="27" t="n"/>
       <c r="J206" s="11">
         <f>SUM(J198:J205)</f>
         <v/>
@@ -28315,15 +29179,15 @@
           <t>x6 — x3</t>
         </is>
       </c>
-      <c r="B209" s="5" t="n"/>
-      <c r="C209" s="5" t="n"/>
-      <c r="D209" s="5" t="n"/>
-      <c r="E209" s="5" t="n"/>
-      <c r="F209" s="5" t="n"/>
-      <c r="G209" s="5" t="n"/>
-      <c r="H209" s="5" t="n"/>
-      <c r="I209" s="5" t="n"/>
-      <c r="J209" s="5" t="n"/>
+      <c r="B209" s="26" t="n"/>
+      <c r="C209" s="26" t="n"/>
+      <c r="D209" s="26" t="n"/>
+      <c r="E209" s="26" t="n"/>
+      <c r="F209" s="26" t="n"/>
+      <c r="G209" s="26" t="n"/>
+      <c r="H209" s="26" t="n"/>
+      <c r="I209" s="26" t="n"/>
+      <c r="J209" s="27" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="6" t="inlineStr">
@@ -28543,14 +29407,14 @@
           <t>IM(x6,x3) =</t>
         </is>
       </c>
-      <c r="B215" s="10" t="n"/>
-      <c r="C215" s="10" t="n"/>
-      <c r="D215" s="10" t="n"/>
-      <c r="E215" s="10" t="n"/>
-      <c r="F215" s="10" t="n"/>
-      <c r="G215" s="10" t="n"/>
-      <c r="H215" s="10" t="n"/>
-      <c r="I215" s="10" t="n"/>
+      <c r="B215" s="26" t="n"/>
+      <c r="C215" s="26" t="n"/>
+      <c r="D215" s="26" t="n"/>
+      <c r="E215" s="26" t="n"/>
+      <c r="F215" s="26" t="n"/>
+      <c r="G215" s="26" t="n"/>
+      <c r="H215" s="26" t="n"/>
+      <c r="I215" s="27" t="n"/>
       <c r="J215" s="11">
         <f>SUM(J211:J214)</f>
         <v/>
@@ -28562,15 +29426,15 @@
           <t>x9 — x3</t>
         </is>
       </c>
-      <c r="B218" s="5" t="n"/>
-      <c r="C218" s="5" t="n"/>
-      <c r="D218" s="5" t="n"/>
-      <c r="E218" s="5" t="n"/>
-      <c r="F218" s="5" t="n"/>
-      <c r="G218" s="5" t="n"/>
-      <c r="H218" s="5" t="n"/>
-      <c r="I218" s="5" t="n"/>
-      <c r="J218" s="5" t="n"/>
+      <c r="B218" s="26" t="n"/>
+      <c r="C218" s="26" t="n"/>
+      <c r="D218" s="26" t="n"/>
+      <c r="E218" s="26" t="n"/>
+      <c r="F218" s="26" t="n"/>
+      <c r="G218" s="26" t="n"/>
+      <c r="H218" s="26" t="n"/>
+      <c r="I218" s="26" t="n"/>
+      <c r="J218" s="27" t="n"/>
     </row>
     <row r="219">
       <c r="A219" s="6" t="inlineStr">
@@ -28950,14 +29814,14 @@
           <t>IM(x9,x3) =</t>
         </is>
       </c>
-      <c r="B228" s="10" t="n"/>
-      <c r="C228" s="10" t="n"/>
-      <c r="D228" s="10" t="n"/>
-      <c r="E228" s="10" t="n"/>
-      <c r="F228" s="10" t="n"/>
-      <c r="G228" s="10" t="n"/>
-      <c r="H228" s="10" t="n"/>
-      <c r="I228" s="10" t="n"/>
+      <c r="B228" s="26" t="n"/>
+      <c r="C228" s="26" t="n"/>
+      <c r="D228" s="26" t="n"/>
+      <c r="E228" s="26" t="n"/>
+      <c r="F228" s="26" t="n"/>
+      <c r="G228" s="26" t="n"/>
+      <c r="H228" s="26" t="n"/>
+      <c r="I228" s="27" t="n"/>
       <c r="J228" s="11">
         <f>SUM(J220:J227)</f>
         <v/>
@@ -28967,8 +29831,8 @@
   <mergeCells count="42">
     <mergeCell ref="A90:I90"/>
     <mergeCell ref="A126:J126"/>
+    <mergeCell ref="A193:I193"/>
     <mergeCell ref="A106:J106"/>
-    <mergeCell ref="A193:I193"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A209:J209"/>
     <mergeCell ref="A165:J165"/>
@@ -29043,18 +29907,17 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
           <t>H(x1)</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n"/>
-      <c r="C4" s="15" t="n"/>
-      <c r="D4" s="15" t="n"/>
-      <c r="E4" s="15" t="n"/>
-      <c r="F4" s="15" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
+      <c r="F4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -29148,19 +30011,17 @@
         <v/>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
           <t>H(x2)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="26" t="n"/>
+      <c r="F11" s="27" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -29254,19 +30115,17 @@
         <v/>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17"/>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
           <t>H(x5)</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n"/>
-      <c r="C18" s="15" t="n"/>
-      <c r="D18" s="15" t="n"/>
-      <c r="E18" s="15" t="n"/>
-      <c r="F18" s="15" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -29381,19 +30240,17 @@
         <v/>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
           <t>H(x4)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
+      <c r="F26" s="27" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -29487,19 +30344,17 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="14" t="inlineStr">
         <is>
           <t>H(x6)</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n"/>
-      <c r="C33" s="15" t="n"/>
-      <c r="D33" s="15" t="n"/>
-      <c r="E33" s="15" t="n"/>
-      <c r="F33" s="15" t="n"/>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+      <c r="E33" s="26" t="n"/>
+      <c r="F33" s="27" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -29593,19 +30448,17 @@
         <v/>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40">
       <c r="A40" s="14" t="inlineStr">
         <is>
           <t>H(x9)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n"/>
-      <c r="C40" s="15" t="n"/>
-      <c r="D40" s="15" t="n"/>
-      <c r="E40" s="15" t="n"/>
-      <c r="F40" s="15" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
+      <c r="F40" s="27" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -29741,19 +30594,17 @@
         <v/>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="14" t="inlineStr">
         <is>
           <t>H(x3)</t>
         </is>
       </c>
-      <c r="B49" s="15" t="n"/>
-      <c r="C49" s="15" t="n"/>
-      <c r="D49" s="15" t="n"/>
-      <c r="E49" s="15" t="n"/>
-      <c r="F49" s="15" t="n"/>
+      <c r="B49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="26" t="n"/>
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="27" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -29889,7 +30740,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -30205,7 +31055,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
@@ -30213,7 +31062,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
@@ -30483,9 +31331,9 @@
           <t>IM(x1,x5) = Σ</t>
         </is>
       </c>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="10" t="n"/>
-      <c r="H12" s="10" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="27" t="n"/>
       <c r="I12" s="11">
         <f>SUM(I6:I11)</f>
         <v/>
@@ -31975,7 +32823,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -32176,17 +33023,16 @@
         <v>2.8092</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>PESO TOTAL MST (Prim)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
-      <c r="C11" s="15" t="n"/>
-      <c r="D11" s="15" t="n"/>
-      <c r="E11" s="15" t="n"/>
+      <c r="B11" s="26" t="n"/>
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="26" t="n"/>
+      <c r="E11" s="27" t="n"/>
       <c r="F11" s="11" t="n">
         <v>2.8092</v>
       </c>
@@ -32222,7 +33068,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -32341,14 +33186,13 @@
         <v>2.8092</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
           <t>PESO TOTAL MST</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n"/>
+      <c r="B11" s="27" t="n"/>
       <c r="C11" s="11" t="n">
         <v>2.8092</v>
       </c>
